--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.631578947368421</v>
+        <v>0.6347826086956522</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6808510638297872</v>
+        <v>0.6197183098591549</v>
       </c>
       <c r="D2">
-        <v>0.4285714285714285</v>
+        <v>0.4251968503937008</v>
       </c>
       <c r="E2">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,16 +420,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6347826086956522</v>
+        <v>0.6260869565217392</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6197183098591549</v>
+        <v>0.6126760563380281</v>
       </c>
       <c r="D2">
-        <v>0.4251968503937008</v>
+        <v>0.4330708661417323</v>
       </c>
       <c r="E2">
         <v>115</v>
